--- a/links/time-series-links_CY25-q2a.xlsx
+++ b/links/time-series-links_CY25-q2a.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca9ccbbb0bd9c947/Documents/post_2020-10/professional/R_projects/Fourier-series/links/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca9ccbbb0bd9c947/Documents/GitHub/Fourier-series/links/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_F25DC773A252ABDACC10489E81DE69C45BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8498374-BF2C-4C82-A619-2025DDB00B53}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_F25DC773A252ABDACC10489E81DE69C45BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FF1407-7558-44CB-B41E-1599AF5945E9}"/>
   <bookViews>
-    <workbookView xWindow="2406" yWindow="2382" windowWidth="18864" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3648" yWindow="396" windowWidth="18858" windowHeight="11136" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="toc" sheetId="2" r:id="rId1"/>
@@ -676,7 +676,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
@@ -769,6 +769,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1446,11 +1449,11 @@
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="33" t="s">
         <v>93</v>
       </c>
       <c r="D6" s="8">
@@ -1482,8 +1485,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A5" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{2C71B353-952D-41F5-B08C-FA2961DD5159}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="82" orientation="landscape" horizontalDpi="4294967294" r:id="rId1"/>
+  <pageSetup scale="82" orientation="landscape" horizontalDpi="4294967294" r:id="rId2"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A
 &amp;F</oddHeader>
